--- a/stories/arbres/ATOM-REL.MOQ.003-06.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Pénélope rentre. À l'école, un camarade a fait tomber son bonnet. Pénélope a ri un peu. Son ventre est serré. Maman l'attend. Papa aussi. Pénélope va raconter. Même si on a ri. Elle dit : maman, j'ai ri. Ce n'était pas gentil. Maman écoute. Papa écoute. Ils disent : merci de raconter. Même si tu as ri.</t>
+          <t>Pénélope rentre. À l'école, un camarade a fait tomber son bonnet. Pénélope a ri un peu. Son ventre est serré. Maman l'attend. Papa aussi. Pénélope va raconter. Même si on a ri. Maman, j'ai ri. Ce n'était pas gentil. Maman écoute. Papa écoute. Ils disent : merci de raconter. Même si tu as ri.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Pénélope rentre. À l'école, un camarade a fait tomber son bonnet. Pénélope a ri un peu. Son ventre est serré. Maman l'attend. Papa aussi. Pénélope va raconter. Même si on a ri.
+narrateur|Maman, j'ai ri. Ce n'était pas gentil. Maman écoute. Papa écoute. Ils disent : merci de raconter. Même si tu as ri.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1487,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Pénélope a ri à l'école. Que fait-elle à la maison ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1660,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Pénélope a raconté. Même si elle a ri. Papa et maman ont écouté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1823,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman prépare le goûter. Pénélope s'assoit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1990,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2030,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.003-06.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1311,6 +1316,7 @@
 narrateur|Maman, j'ai ri. Ce n'était pas gentil. Maman écoute. Papa écoute. Ils disent : merci de raconter. Même si tu as ri.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1494,6 +1500,7 @@
           <t>narrateur|Pénélope a ri à l'école. Que fait-elle à la maison ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1665,6 +1672,7 @@
           <t>narrateur|Pénélope a raconté. Même si elle a ri. Papa et maman ont écouté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1828,6 +1836,7 @@
           <t>narrateur|Maman prépare le goûter. Pénélope s'assoit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1995,6 +2004,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2013,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2037,6 +2047,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2238,6 +2262,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.MOQ.003-06.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pénélope raconte, même si elle a ri</t>
+          <t>Le paillasson bleu de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le chat dort sur le paillasson bleu. Mila rentre. Même si elle a ri à l'école, elle raconte à maman et papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Pénélope rentre. À l'école, un camarade a fait tomber son bonnet. Pénélope a ri un peu. Son ventre est serré. Maman l'attend. Papa aussi. Pénélope va raconter. Même si on a ri. Maman, j'ai ri. Ce n'était pas gentil. Maman écoute. Papa écoute. Ils disent : merci de raconter. Même si tu as ri.</t>
+          <t>Le chat dort sur le paillasson bleu. Sa fourrure grise est toute ronde. Le miel coule lentement sur le toast. Ça sent le chaud et le sucré. La porte bleue laisse entrer un peu d'air. Un oiseau picore dans la haie. Le miel fait un fil d'or, tout fin. La poignée de la porte est un peu froide. Le toast est prêt, Mila. Le chat n'a pas bougé. Il t'attendait. En ce moment, Mila rentre de l'école. Son cartable frôle le paillasson. Le chat ouvre un œil, puis se rendort. Mila a les joues chaudes. Son ventre est serré. À l'école, un bonnet est tombé par terre. Il y a eu des rires. Mila a ri un peu aussi. Maman. J'ai ri. Ce n'était pas gentil. Je t'écoute. Viens près de la table. Moi aussi, je t'écoute. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. Un bonnet est tombé. On a ri. J'ai ri un peu. Mila ne répète pas les mots. Elle parle tout bas, près du toast. Même si tu as ri, tu racontes. Même si on a ri, on raconte à papa ou maman. Merci d'avoir raconté. On est là. Mon ventre est encore un peu serré. Souffle un peu. Mila souffle. Ses épaules descendent. Bravo, Mila. C'est du bon travail. Tu as dit ce qui s'est passé. Tu veux ton toast au miel ? Oui, maman. Le miel colle un peu à son doigt. Le chat ronronne sur le paillasson. On reste encore un peu ensemble ? Oui, papa. La porte bleue peut se fermer, maintenant. Mila boit une gorgée d'eau. Elle se sent plus légère. L'oiseau s'est tu, dans la haie. Tu as raconté. Même si tu as ri. Oui, maman. On est là, ce soir aussi. Le chat change encore de patte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,8 +1324,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Pénélope rentre. À l'école, un camarade a fait tomber son bonnet. Pénélope a ri un peu. Son ventre est serré. Maman l'attend. Papa aussi. Pénélope va raconter. Même si on a ri.
-narrateur|Maman, j'ai ri. Ce n'était pas gentil. Maman écoute. Papa écoute. Ils disent : merci de raconter. Même si tu as ri.</t>
+          <t>narrateur|Le chat dort sur le paillasson bleu.
+narrateur|Sa fourrure grise est toute ronde.
+narrateur|Le miel coule lentement sur le toast.
+narrateur|Ça sent le chaud et le sucré.
+narrateur|La porte bleue laisse entrer un peu d'air.
+narrateur|Un oiseau picore dans la haie.
+narrateur|Le miel fait un fil d'or, tout fin.
+narrateur|La poignée de la porte est un peu froide.
+maman|Le toast est prêt, Mila.
+papa|Le chat n'a pas bougé.
+papa|Il t'attendait.
+narrateur|En ce moment, Mila rentre de l'école.
+narrateur|Son cartable frôle le paillasson.
+narrateur|Le chat ouvre un œil, puis se rendort.
+narrateur|Mila a les joues chaudes.
+narrateur|Son ventre est serré.
+narrateur|À l'école, un bonnet est tombé par terre.
+narrateur|Il y a eu des rires.
+narrateur|Mila a ri un peu aussi.
+enfant-f|Maman.
+enfant-f|J'ai ri.
+enfant-f|Ce n'était pas gentil.
+maman|Je t'écoute.
+maman|Viens près de la table.
+papa|Moi aussi, je t'écoute.
+papa|Tu peux raconter.
+papa|Raconter, c'est dire ce qui s'est passé.
+enfant-f|Un bonnet est tombé.
+enfant-f|On a ri.
+enfant-f|J'ai ri un peu.
+narrateur|Mila ne répète pas les mots.
+narrateur|Elle parle tout bas, près du toast.
+maman|Même si tu as ri, tu racontes.
+papa|Même si on a ri, on raconte à papa ou maman.
+maman|Merci d'avoir raconté.
+papa|On est là.
+enfant-f|Mon ventre est encore un peu serré.
+maman|Souffle un peu.
+narrateur|Mila souffle.
+narrateur|Ses épaules descendent.
+papa|Bravo, Mila.
+papa|C'est du bon travail.
+maman|Tu as dit ce qui s'est passé.
+maman|Tu veux ton toast au miel ?
+enfant-f|Oui, maman.
+narrateur|Le miel colle un peu à son doigt.
+narrateur|Le chat ronronne sur le paillasson.
+papa|On reste encore un peu ensemble ?
+enfant-f|Oui, papa.
+maman|La porte bleue peut se fermer, maintenant.
+narrateur|Mila boit une gorgée d'eau.
+narrateur|Elle se sent plus légère.
+narrateur|L'oiseau s'est tu, dans la haie.
+maman|Tu as raconté.
+maman|Même si tu as ri.
+enfant-f|Oui, maman.
+papa|On est là, ce soir aussi.
+narrateur|Le chat change encore de patte.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1341,7 +1409,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Pénélope a ri à l'école. Que fait-elle à la maison ?</t>
+          <t>Mila a ri à l'école. Que fait-elle à la maison ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1497,7 +1565,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Pénélope a ri à l'école. Que fait-elle à la maison ?</t>
+          <t>narrateur|Mila a ri à l'école.
+narrateur|Que fait-elle à la maison ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1525,7 +1594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Pénélope a raconté. Même si elle a ri. Papa et maman ont écouté.</t>
+          <t>Mila a raconté. Même si elle a ri. Papa et maman ont écouté. Tu es venue nous le dire. Bravo. C'est du bon travail, Mila. J'ai raconté. Même si j'ai ri. Oui. On raconte à papa ou maman. Le miel brille encore sur le toast. Le ventre de Mila se desserre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1669,7 +1738,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Pénélope a raconté. Même si elle a ri. Papa et maman ont écouté.</t>
+          <t>narrateur|Mila a raconté.
+narrateur|Même si elle a ri.
+narrateur|Papa et maman ont écouté.
+maman|Tu es venue nous le dire.
+maman|Bravo.
+papa|C'est du bon travail, Mila.
+enfant-f|J'ai raconté.
+enfant-f|Même si j'ai ri.
+papa|Oui.
+papa|On raconte à papa ou maman.
+narrateur|Le miel brille encore sur le toast.
+narrateur|Le ventre de Mila se desserre.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1697,7 +1777,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman prépare le goûter. Pénélope s'assoit.</t>
+          <t>Maman prépare le goûter. Une seconde tranche attend près du miel. Tu t'assois ? Oui. Mila s'assoit. Le chat change de patte, sans se réveiller. Le toast t'a plu ? Oui, papa. On t'écoute encore, si tu veux. J'ai déjà raconté. C'est bien. Le paillasson bleu reste tout rond sous le chat.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1913,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman prépare le goûter. Pénélope s'assoit.</t>
+          <t>narrateur|Maman prépare le goûter.
+narrateur|Une seconde tranche attend près du miel.
+maman|Tu t'assois ?
+enfant-f|Oui.
+narrateur|Mila s'assoit.
+narrateur|Le chat change de patte, sans se réveiller.
+papa|Le toast t'a plu ?
+enfant-f|Oui, papa.
+maman|On t'écoute encore, si tu veux.
+enfant-f|J'ai déjà raconté.
+papa|C'est bien.
+narrateur|Le paillasson bleu reste tout rond sous le chat.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1861,7 +1952,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai raconté à la maison. Même si j'ai ri. Bravo. Tu as fait du bon travail. On t'a écouté. Le chat dort encore sur le paillasson bleu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2001,7 +2092,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai raconté à la maison.
+enfant-f|Même si j'ai ri.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+papa|On t'a écouté.
+narrateur|Le chat dort encore sur le paillasson bleu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2023,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2061,6 +2158,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.003-06.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le chat dort sur le paillasson bleu. Sa fourrure grise est toute ronde. Le miel coule lentement sur le toast. Ça sent le chaud et le sucré. La porte bleue laisse entrer un peu d'air. Un oiseau picore dans la haie. Le miel fait un fil d'or, tout fin. La poignée de la porte est un peu froide. Le toast est prêt, Mila. Le chat n'a pas bougé. Il t'attendait. En ce moment, Mila rentre de l'école. Son cartable frôle le paillasson. Le chat ouvre un œil, puis se rendort. Mila a les joues chaudes. Son ventre est serré. À l'école, un bonnet est tombé par terre. Il y a eu des rires. Mila a ri un peu aussi. Maman. J'ai ri. Ce n'était pas gentil. Je t'écoute. Viens près de la table. Moi aussi, je t'écoute. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. Un bonnet est tombé. On a ri. J'ai ri un peu. Mila ne répète pas les mots. Elle parle tout bas, près du toast. Même si tu as ri, tu racontes. Même si on a ri, on raconte à papa ou maman. Merci d'avoir raconté. On est là. Mon ventre est encore un peu serré. Souffle un peu. Mila souffle. Ses épaules descendent. Bravo, Mila. C'est du bon travail. Tu as dit ce qui s'est passé. Tu veux ton toast au miel ? Oui, maman. Le miel colle un peu à son doigt. Le chat ronronne sur le paillasson. On reste encore un peu ensemble ? Oui, papa. La porte bleue peut se fermer, maintenant. Mila boit une gorgée d'eau. Elle se sent plus légère. L'oiseau s'est tu, dans la haie. Tu as raconté. Même si tu as ri. Oui, maman. On est là, ce soir aussi. Le chat change encore de patte.</t>
+          <t>Le chat dort sur le paillasson bleu. Sa fourrure grise est toute ronde. Le miel coule lentement sur le toast. Ça sent le chaud et le sucré. La porte bleue laisse entrer un peu d'air. Un oiseau picore dans la haie. Le miel fait un fil d'or, tout fin. La poignée de la porte est un peu froide. Le toast est prêt, Mila. Le chat n'a pas bougé. Il t'attendait. En ce moment, Mila rentre de l'école. Son cartable frôle le paillasson. Le chat ouvre un œil, puis se rendort. Mila a les joues chaudes. Son ventre est serré. À l'école, un bonnet est tombé par terre. Il y a eu des rires. Mila a ri un peu aussi. Maman. J'ai ri. Ce n'était pas gentil. Je t'écoute. Viens près de la table. Moi aussi, je t'écoute. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. Un bonnet est tombé. On a ri. J'ai ri un peu. Mila ne répète pas les mots. Elle parle tout bas, près du toast. Même si tu as ri, tu racontes. Même si on a ri, on raconte à papa ou maman. Merci d'avoir raconté. On est là. Mon ventre est encore un peu serré. Souffle un peu. Mila souffle. Ses épaules descendent. Bravo, Mila. Tu as dit ce qui s'est passé. Tu veux ton toast au miel ? Oui, maman. Le miel colle un peu à son doigt. Le chat ronronne sur le paillasson. On reste encore un peu ensemble ? Oui, papa. La porte bleue peut se fermer, maintenant. Mila boit une gorgée d'eau. Elle se sent plus légère. L'oiseau s'est tu, dans la haie. Tu as raconté. Même si tu as ri. Oui, maman. On est là, ce soir aussi. Le chat change encore de patte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Pénélope rentre. À l'école, un camarade a fait tomber son bonnet. Pénélope a ri un peu. Son ventre est serré. Maman l'attend. Papa aussi. Pénélope va &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;. Même si on a ri. Elle dit : maman, j'ai ri. Ce n'était pas gentil. Maman écoute. Papa écoute. Ils disent : merci de raconter. Même si tu as ri.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le chat dort sur le paillasson bleu. Sa fourrure grise est toute ronde. Le miel coule lentement sur le toast. Ça sent le chaud et le sucré. La porte bleue laisse entrer un peu d'air. Un oiseau picore dans la haie. Le miel fait un fil d'or, tout fin. La poignée de la porte est un peu froide. Le toast est prêt, Mila. Le chat n'a pas bougé. Il t'attendait. En ce moment, Mila rentre de l'école. Son cartable frôle le paillasson. Le chat ouvre un œil, puis se rendort. Mila a les joues chaudes. Son ventre est serré. À l'école, un bonnet est tombé par terre. Il y a eu des rires. Mila a ri un peu aussi. Maman. J'ai ri. Ce n'était pas gentil. Je t'écoute. Viens près de la table. Moi aussi, je t'écoute. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. Un bonnet est tombé. On a ri. J'ai ri un peu. Mila ne répète pas les mots. Elle parle tout bas, près du toast. Même si tu as ri, tu racontes. Même si on a ri, on raconte à papa ou maman. Merci d'avoir raconté. On est là. Mon ventre est encore un peu serré. Souffle un peu. Mila souffle. Ses épaules descendent. Bravo, Mila. Tu as dit ce qui s'est passé. Tu veux ton toast au miel ? Oui, maman. Le miel colle un peu à son doigt. Le chat ronronne sur le paillasson. On reste encore un peu ensemble ? Oui, papa. La porte bleue peut se fermer, maintenant. Mila boit une gorgée d'eau. Elle se sent plus légère. L'oiseau s'est tu, dans la haie. Tu as raconté. Même si tu as ri. Oui, maman. On est là, ce soir aussi. Le chat change encore de patte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1365,7 +1365,6 @@
 narrateur|Mila souffle.
 narrateur|Ses épaules descendent.
 papa|Bravo, Mila.
-papa|C'est du bon travail.
 maman|Tu as dit ce qui s'est passé.
 maman|Tu veux ton toast au miel ?
 enfant-f|Oui, maman.
@@ -1384,7 +1383,6 @@
 narrateur|Le chat change encore de patte.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1414,7 +1412,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Pénélope a ri à l'école. Que fait-elle à la maison ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a ri à l'école. Que fait-elle à la maison ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1569,7 +1567,6 @@
 narrateur|Que fait-elle à la maison ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1594,12 +1591,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a raconté. Même si elle a ri. Papa et maman ont écouté. Tu es venue nous le dire. Bravo. C'est du bon travail, Mila. J'ai raconté. Même si j'ai ri. Oui. On raconte à papa ou maman. Le miel brille encore sur le toast. Le ventre de Mila se desserre.</t>
+          <t>Mila a raconté. Même si elle a ri. Papa et maman ont écouté. Tu es venue nous le dire. Bravo. J'ai raconté. Même si j'ai ri. Oui. On raconte à papa ou maman. Le miel brille encore sur le toast. Le ventre de Mila se desserre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Pénélope a raconté. &lt;emphasis level="moderate"&gt;même&lt;/emphasis&gt; si elle a ri. Papa et maman ont écouté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a raconté. Même si elle a ri. Papa et maman ont écouté. Tu es venue nous le dire. Bravo. J'ai raconté. Même si j'ai ri. Oui. On raconte à papa ou maman. Le miel brille encore sur le toast. Le ventre de Mila se desserre.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1743,7 +1740,6 @@
 narrateur|Papa et maman ont écouté.
 maman|Tu es venue nous le dire.
 maman|Bravo.
-papa|C'est du bon travail, Mila.
 enfant-f|J'ai raconté.
 enfant-f|Même si j'ai ri.
 papa|Oui.
@@ -1752,7 +1748,6 @@
 narrateur|Le ventre de Mila se desserre.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1782,7 +1777,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman prépare le goûter. Pénélope s'assoit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman prépare le goûter. Une seconde tranche attend près du miel. Tu t'assois ? Oui. Mila s'assoit. Le chat change de patte, sans se réveiller. Le toast t'a plu ? Oui, papa. On t'écoute encore, si tu veux. J'ai déjà raconté. C'est bien. Le paillasson bleu reste tout rond sous le chat.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1927,7 +1922,6 @@
 narrateur|Le paillasson bleu reste tout rond sous le chat.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1952,12 +1946,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai raconté à la maison. Même si j'ai ri. Bravo. Tu as fait du bon travail. On t'a écouté. Le chat dort encore sur le paillasson bleu. L'histoire est finie.</t>
+          <t>J'ai raconté à la maison. Même si j'ai ri. Bravo. On t'a écouté. Le chat dort encore sur le paillasson bleu.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai raconté à la maison. Même si j'ai ri. Bravo. On t'a écouté. Le chat dort encore sur le paillasson bleu.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2095,13 +2089,10 @@
           <t>enfant-f|J'ai raconté à la maison.
 enfant-f|Même si j'ai ri.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 papa|On t'a écouté.
-narrateur|Le chat dort encore sur le paillasson bleu.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le chat dort encore sur le paillasson bleu.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2120,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2165,6 +2156,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.003-06.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-06.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pénélope, maman, papa</t>
+          <t>Mila, maman, papa</t>
         </is>
       </c>
     </row>
